--- a/summary output/point_labels_all.xlsx
+++ b/summary output/point_labels_all.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I692"/>
+  <dimension ref="A1:J692"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -400,6 +400,11 @@
           <t>brush</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>residual</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -445,6 +450,9 @@
           <t>b</t>
         </is>
       </c>
+      <c r="J2">
+        <v>55</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -490,6 +498,9 @@
           <t>b</t>
         </is>
       </c>
+      <c r="J3">
+        <v>55</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -535,6 +546,9 @@
           <t>b</t>
         </is>
       </c>
+      <c r="J4">
+        <v>55</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -580,6 +594,9 @@
           <t>b</t>
         </is>
       </c>
+      <c r="J5">
+        <v>55</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -625,6 +642,9 @@
           <t>b</t>
         </is>
       </c>
+      <c r="J6">
+        <v>55</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -670,6 +690,9 @@
           <t>b</t>
         </is>
       </c>
+      <c r="J7">
+        <v>27</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -715,6 +738,9 @@
           <t>b</t>
         </is>
       </c>
+      <c r="J8">
+        <v>27</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -760,6 +786,9 @@
           <t>b</t>
         </is>
       </c>
+      <c r="J9">
+        <v>27</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -805,6 +834,9 @@
           <t>b</t>
         </is>
       </c>
+      <c r="J10">
+        <v>27</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -850,6 +882,9 @@
           <t>b</t>
         </is>
       </c>
+      <c r="J11">
+        <v>27</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -895,6 +930,9 @@
           <t>u</t>
         </is>
       </c>
+      <c r="J12">
+        <v>55</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -940,6 +978,9 @@
           <t>u</t>
         </is>
       </c>
+      <c r="J13">
+        <v>55</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -985,6 +1026,9 @@
           <t>u</t>
         </is>
       </c>
+      <c r="J14">
+        <v>55</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1030,6 +1074,9 @@
           <t>u</t>
         </is>
       </c>
+      <c r="J15">
+        <v>55</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1075,6 +1122,9 @@
           <t>u</t>
         </is>
       </c>
+      <c r="J16">
+        <v>55</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1120,6 +1170,9 @@
           <t>b</t>
         </is>
       </c>
+      <c r="J17">
+        <v>27</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1165,6 +1218,9 @@
           <t>b</t>
         </is>
       </c>
+      <c r="J18">
+        <v>27</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1210,6 +1266,9 @@
           <t>b</t>
         </is>
       </c>
+      <c r="J19">
+        <v>27</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1255,6 +1314,9 @@
           <t>b</t>
         </is>
       </c>
+      <c r="J20">
+        <v>27</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1300,6 +1362,9 @@
           <t>b</t>
         </is>
       </c>
+      <c r="J21">
+        <v>27</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1345,6 +1410,9 @@
           <t>u</t>
         </is>
       </c>
+      <c r="J22">
+        <v>27</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1390,6 +1458,9 @@
           <t>u</t>
         </is>
       </c>
+      <c r="J23">
+        <v>27</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1435,6 +1506,9 @@
           <t>u</t>
         </is>
       </c>
+      <c r="J24">
+        <v>27</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1480,6 +1554,9 @@
           <t>u</t>
         </is>
       </c>
+      <c r="J25">
+        <v>27</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1525,6 +1602,9 @@
           <t>u</t>
         </is>
       </c>
+      <c r="J26">
+        <v>27</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1570,6 +1650,9 @@
           <t>b</t>
         </is>
       </c>
+      <c r="J27">
+        <v>27</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1615,6 +1698,9 @@
           <t>b</t>
         </is>
       </c>
+      <c r="J28">
+        <v>27</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1660,6 +1746,9 @@
           <t>b</t>
         </is>
       </c>
+      <c r="J29">
+        <v>27</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1705,6 +1794,9 @@
           <t>b</t>
         </is>
       </c>
+      <c r="J30">
+        <v>27</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1750,6 +1842,9 @@
           <t>b</t>
         </is>
       </c>
+      <c r="J31">
+        <v>27</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1795,6 +1890,9 @@
           <t>u</t>
         </is>
       </c>
+      <c r="J32">
+        <v>27</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1840,6 +1938,9 @@
           <t>u</t>
         </is>
       </c>
+      <c r="J33">
+        <v>27</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1885,6 +1986,9 @@
           <t>u</t>
         </is>
       </c>
+      <c r="J34">
+        <v>27</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1930,6 +2034,9 @@
           <t>u</t>
         </is>
       </c>
+      <c r="J35">
+        <v>27</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1975,6 +2082,9 @@
           <t>u</t>
         </is>
       </c>
+      <c r="J36">
+        <v>27</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2020,6 +2130,9 @@
           <t>u</t>
         </is>
       </c>
+      <c r="J37">
+        <v>27</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2065,6 +2178,9 @@
           <t>u</t>
         </is>
       </c>
+      <c r="J38">
+        <v>27</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2110,6 +2226,9 @@
           <t>u</t>
         </is>
       </c>
+      <c r="J39">
+        <v>27</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2155,6 +2274,9 @@
           <t>u</t>
         </is>
       </c>
+      <c r="J40">
+        <v>27</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2200,6 +2322,9 @@
           <t>u</t>
         </is>
       </c>
+      <c r="J41">
+        <v>27</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2245,6 +2370,9 @@
           <t>b</t>
         </is>
       </c>
+      <c r="J42">
+        <v>27</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2290,6 +2418,9 @@
           <t>b</t>
         </is>
       </c>
+      <c r="J43">
+        <v>27</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2335,6 +2466,9 @@
           <t>b</t>
         </is>
       </c>
+      <c r="J44">
+        <v>27</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2380,6 +2514,9 @@
           <t>b</t>
         </is>
       </c>
+      <c r="J45">
+        <v>27</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2425,6 +2562,9 @@
           <t>b</t>
         </is>
       </c>
+      <c r="J46">
+        <v>27</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2470,6 +2610,9 @@
           <t>u</t>
         </is>
       </c>
+      <c r="J47">
+        <v>55</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2515,6 +2658,9 @@
           <t>u</t>
         </is>
       </c>
+      <c r="J48">
+        <v>55</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2560,6 +2706,9 @@
           <t>u</t>
         </is>
       </c>
+      <c r="J49">
+        <v>55</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2605,6 +2754,9 @@
           <t>u</t>
         </is>
       </c>
+      <c r="J50">
+        <v>55</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2650,6 +2802,9 @@
           <t>u</t>
         </is>
       </c>
+      <c r="J51">
+        <v>55</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2695,6 +2850,9 @@
           <t>b</t>
         </is>
       </c>
+      <c r="J52">
+        <v>55</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2740,6 +2898,9 @@
           <t>b</t>
         </is>
       </c>
+      <c r="J53">
+        <v>55</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2785,6 +2946,9 @@
           <t>b</t>
         </is>
       </c>
+      <c r="J54">
+        <v>55</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2830,6 +2994,9 @@
           <t>b</t>
         </is>
       </c>
+      <c r="J55">
+        <v>55</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2875,6 +3042,9 @@
           <t>b</t>
         </is>
       </c>
+      <c r="J56">
+        <v>55</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2920,6 +3090,9 @@
           <t>b</t>
         </is>
       </c>
+      <c r="J57">
+        <v>55</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2965,6 +3138,9 @@
           <t>b</t>
         </is>
       </c>
+      <c r="J58">
+        <v>55</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3010,6 +3186,9 @@
           <t>b</t>
         </is>
       </c>
+      <c r="J59">
+        <v>55</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3055,6 +3234,9 @@
           <t>b</t>
         </is>
       </c>
+      <c r="J60">
+        <v>55</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3100,6 +3282,9 @@
           <t>b</t>
         </is>
       </c>
+      <c r="J61">
+        <v>55</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3145,6 +3330,9 @@
           <t>u</t>
         </is>
       </c>
+      <c r="J62">
+        <v>55</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3190,6 +3378,9 @@
           <t>u</t>
         </is>
       </c>
+      <c r="J63">
+        <v>55</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3235,6 +3426,9 @@
           <t>u</t>
         </is>
       </c>
+      <c r="J64">
+        <v>55</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3280,6 +3474,9 @@
           <t>u</t>
         </is>
       </c>
+      <c r="J65">
+        <v>55</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3325,6 +3522,9 @@
           <t>u</t>
         </is>
       </c>
+      <c r="J66">
+        <v>55</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3370,6 +3570,9 @@
           <t>b</t>
         </is>
       </c>
+      <c r="J67">
+        <v>55</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3415,6 +3618,9 @@
           <t>b</t>
         </is>
       </c>
+      <c r="J68">
+        <v>55</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3460,6 +3666,9 @@
           <t>b</t>
         </is>
       </c>
+      <c r="J69">
+        <v>55</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3505,6 +3714,9 @@
           <t>b</t>
         </is>
       </c>
+      <c r="J70">
+        <v>55</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3550,6 +3762,9 @@
           <t>b</t>
         </is>
       </c>
+      <c r="J71">
+        <v>55</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3595,6 +3810,9 @@
           <t>u</t>
         </is>
       </c>
+      <c r="J72">
+        <v>55</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3640,6 +3858,9 @@
           <t>u</t>
         </is>
       </c>
+      <c r="J73">
+        <v>55</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3685,6 +3906,9 @@
           <t>u</t>
         </is>
       </c>
+      <c r="J74">
+        <v>55</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3730,6 +3954,9 @@
           <t>u</t>
         </is>
       </c>
+      <c r="J75">
+        <v>55</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3775,6 +4002,9 @@
           <t>u</t>
         </is>
       </c>
+      <c r="J76">
+        <v>55</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3820,6 +4050,9 @@
           <t>u</t>
         </is>
       </c>
+      <c r="J77">
+        <v>55</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3865,6 +4098,9 @@
           <t>u</t>
         </is>
       </c>
+      <c r="J78">
+        <v>55</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3910,6 +4146,9 @@
           <t>u</t>
         </is>
       </c>
+      <c r="J79">
+        <v>55</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3955,6 +4194,9 @@
           <t>u</t>
         </is>
       </c>
+      <c r="J80">
+        <v>55</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -4000,6 +4242,9 @@
           <t>u</t>
         </is>
       </c>
+      <c r="J81">
+        <v>55</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -4045,6 +4290,9 @@
           <t>b</t>
         </is>
       </c>
+      <c r="J82">
+        <v>55</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -4090,6 +4338,9 @@
           <t>b</t>
         </is>
       </c>
+      <c r="J83">
+        <v>55</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -4135,6 +4386,9 @@
           <t>b</t>
         </is>
       </c>
+      <c r="J84">
+        <v>55</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -4180,6 +4434,9 @@
           <t>b</t>
         </is>
       </c>
+      <c r="J85">
+        <v>55</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -4225,6 +4482,9 @@
           <t>b</t>
         </is>
       </c>
+      <c r="J86">
+        <v>55</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -4270,6 +4530,9 @@
           <t>u</t>
         </is>
       </c>
+      <c r="J87">
+        <v>27</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -4315,6 +4578,9 @@
           <t>u</t>
         </is>
       </c>
+      <c r="J88">
+        <v>27</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -4360,6 +4626,9 @@
           <t>u</t>
         </is>
       </c>
+      <c r="J89">
+        <v>27</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -4405,6 +4674,9 @@
           <t>u</t>
         </is>
       </c>
+      <c r="J90">
+        <v>27</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -4450,6 +4722,9 @@
           <t>u</t>
         </is>
       </c>
+      <c r="J91">
+        <v>27</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -4495,6 +4770,9 @@
           <t>b</t>
         </is>
       </c>
+      <c r="J92">
+        <v>27</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -4540,6 +4818,9 @@
           <t>b</t>
         </is>
       </c>
+      <c r="J93">
+        <v>27</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -4585,6 +4866,9 @@
           <t>b</t>
         </is>
       </c>
+      <c r="J94">
+        <v>27</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -4630,6 +4914,9 @@
           <t>b</t>
         </is>
       </c>
+      <c r="J95">
+        <v>27</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -4675,6 +4962,9 @@
           <t>b</t>
         </is>
       </c>
+      <c r="J96">
+        <v>27</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -4720,6 +5010,9 @@
           <t>u</t>
         </is>
       </c>
+      <c r="J97">
+        <v>27</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -4765,6 +5058,9 @@
           <t>u</t>
         </is>
       </c>
+      <c r="J98">
+        <v>27</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -4810,6 +5106,9 @@
           <t>u</t>
         </is>
       </c>
+      <c r="J99">
+        <v>27</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -4855,6 +5154,9 @@
           <t>u</t>
         </is>
       </c>
+      <c r="J100">
+        <v>27</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -4900,6 +5202,9 @@
           <t>u</t>
         </is>
       </c>
+      <c r="J101">
+        <v>27</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -4945,6 +5250,9 @@
           <t>u</t>
         </is>
       </c>
+      <c r="J102">
+        <v>27</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -4990,6 +5298,9 @@
           <t>u</t>
         </is>
       </c>
+      <c r="J103">
+        <v>27</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -5035,6 +5346,9 @@
           <t>u</t>
         </is>
       </c>
+      <c r="J104">
+        <v>27</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -5080,6 +5394,9 @@
           <t>u</t>
         </is>
       </c>
+      <c r="J105">
+        <v>27</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -5125,6 +5442,9 @@
           <t>u</t>
         </is>
       </c>
+      <c r="J106">
+        <v>27</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -5170,6 +5490,9 @@
           <t>u</t>
         </is>
       </c>
+      <c r="J107">
+        <v>55</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -5215,6 +5538,9 @@
           <t>u</t>
         </is>
       </c>
+      <c r="J108">
+        <v>55</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -5260,6 +5586,9 @@
           <t>u</t>
         </is>
       </c>
+      <c r="J109">
+        <v>55</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -5305,6 +5634,9 @@
           <t>u</t>
         </is>
       </c>
+      <c r="J110">
+        <v>55</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -5350,6 +5682,9 @@
           <t>u</t>
         </is>
       </c>
+      <c r="J111">
+        <v>55</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -5395,6 +5730,9 @@
           <t>u</t>
         </is>
       </c>
+      <c r="J112">
+        <v>55</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -5440,6 +5778,9 @@
           <t>u</t>
         </is>
       </c>
+      <c r="J113">
+        <v>55</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -5485,6 +5826,9 @@
           <t>u</t>
         </is>
       </c>
+      <c r="J114">
+        <v>55</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -5530,6 +5874,9 @@
           <t>u</t>
         </is>
       </c>
+      <c r="J115">
+        <v>55</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -5575,6 +5922,9 @@
           <t>u</t>
         </is>
       </c>
+      <c r="J116">
+        <v>55</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -5620,6 +5970,9 @@
           <t>u</t>
         </is>
       </c>
+      <c r="J117">
+        <v>55</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -5665,6 +6018,9 @@
           <t>u</t>
         </is>
       </c>
+      <c r="J118">
+        <v>55</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -5710,6 +6066,9 @@
           <t>u</t>
         </is>
       </c>
+      <c r="J119">
+        <v>55</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -5755,6 +6114,9 @@
           <t>u</t>
         </is>
       </c>
+      <c r="J120">
+        <v>55</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -5800,6 +6162,9 @@
           <t>u</t>
         </is>
       </c>
+      <c r="J121">
+        <v>55</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -5845,6 +6210,9 @@
           <t>u</t>
         </is>
       </c>
+      <c r="J122">
+        <v>27</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -5890,6 +6258,9 @@
           <t>b</t>
         </is>
       </c>
+      <c r="J123">
+        <v>27</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -5935,6 +6306,9 @@
           <t>b</t>
         </is>
       </c>
+      <c r="J124">
+        <v>27</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -5980,6 +6354,9 @@
           <t>b</t>
         </is>
       </c>
+      <c r="J125">
+        <v>27</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -6025,6 +6402,9 @@
           <t>b</t>
         </is>
       </c>
+      <c r="J126">
+        <v>27</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -6070,6 +6450,9 @@
           <t>b</t>
         </is>
       </c>
+      <c r="J127">
+        <v>27</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -6115,6 +6498,9 @@
           <t>u</t>
         </is>
       </c>
+      <c r="J128">
+        <v>27</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -6160,6 +6546,9 @@
           <t>u</t>
         </is>
       </c>
+      <c r="J129">
+        <v>27</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -6205,6 +6594,9 @@
           <t>u</t>
         </is>
       </c>
+      <c r="J130">
+        <v>27</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -6250,6 +6642,9 @@
           <t>u</t>
         </is>
       </c>
+      <c r="J131">
+        <v>27</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -6295,6 +6690,9 @@
           <t>u</t>
         </is>
       </c>
+      <c r="J132">
+        <v>55</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -6340,6 +6738,9 @@
           <t>u</t>
         </is>
       </c>
+      <c r="J133">
+        <v>55</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -6385,6 +6786,9 @@
           <t>u</t>
         </is>
       </c>
+      <c r="J134">
+        <v>55</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -6430,6 +6834,9 @@
           <t>u</t>
         </is>
       </c>
+      <c r="J135">
+        <v>55</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -6475,6 +6882,9 @@
           <t>u</t>
         </is>
       </c>
+      <c r="J136">
+        <v>55</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -6520,6 +6930,9 @@
           <t>b</t>
         </is>
       </c>
+      <c r="J137">
+        <v>55</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -6565,6 +6978,9 @@
           <t>b</t>
         </is>
       </c>
+      <c r="J138">
+        <v>55</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -6610,6 +7026,9 @@
           <t>b</t>
         </is>
       </c>
+      <c r="J139">
+        <v>55</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -6655,6 +7074,9 @@
           <t>b</t>
         </is>
       </c>
+      <c r="J140">
+        <v>55</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -6700,6 +7122,9 @@
           <t>b</t>
         </is>
       </c>
+      <c r="J141">
+        <v>55</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -6745,6 +7170,9 @@
           <t>b</t>
         </is>
       </c>
+      <c r="J142">
+        <v>55</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -6790,6 +7218,9 @@
           <t>b</t>
         </is>
       </c>
+      <c r="J143">
+        <v>55</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -6835,6 +7266,9 @@
           <t>b</t>
         </is>
       </c>
+      <c r="J144">
+        <v>55</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -6880,6 +7314,9 @@
           <t>b</t>
         </is>
       </c>
+      <c r="J145">
+        <v>55</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -6925,6 +7362,9 @@
           <t>b</t>
         </is>
       </c>
+      <c r="J146">
+        <v>55</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -6970,6 +7410,9 @@
           <t>u</t>
         </is>
       </c>
+      <c r="J147">
+        <v>55</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -7015,6 +7458,9 @@
           <t>u</t>
         </is>
       </c>
+      <c r="J148">
+        <v>55</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -7060,6 +7506,9 @@
           <t>u</t>
         </is>
       </c>
+      <c r="J149">
+        <v>55</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -7105,6 +7554,9 @@
           <t>u</t>
         </is>
       </c>
+      <c r="J150">
+        <v>55</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -7150,6 +7602,9 @@
           <t>u</t>
         </is>
       </c>
+      <c r="J151">
+        <v>55</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -7195,6 +7650,9 @@
           <t>b</t>
         </is>
       </c>
+      <c r="J152">
+        <v>27</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -7240,6 +7698,9 @@
           <t>b</t>
         </is>
       </c>
+      <c r="J153">
+        <v>27</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -7285,6 +7746,9 @@
           <t>b</t>
         </is>
       </c>
+      <c r="J154">
+        <v>27</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -7330,6 +7794,9 @@
           <t>b</t>
         </is>
       </c>
+      <c r="J155">
+        <v>27</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -7375,6 +7842,9 @@
           <t>b</t>
         </is>
       </c>
+      <c r="J156">
+        <v>27</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -7420,6 +7890,9 @@
           <t>u</t>
         </is>
       </c>
+      <c r="J157">
+        <v>27</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -7465,6 +7938,9 @@
           <t>u</t>
         </is>
       </c>
+      <c r="J158">
+        <v>27</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -7510,6 +7986,9 @@
           <t>u</t>
         </is>
       </c>
+      <c r="J159">
+        <v>27</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -7555,6 +8034,9 @@
           <t>u</t>
         </is>
       </c>
+      <c r="J160">
+        <v>27</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -7600,6 +8082,9 @@
           <t>u</t>
         </is>
       </c>
+      <c r="J161">
+        <v>27</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -7645,6 +8130,9 @@
           <t>b</t>
         </is>
       </c>
+      <c r="J162">
+        <v>27</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -7690,6 +8178,9 @@
           <t>b</t>
         </is>
       </c>
+      <c r="J163">
+        <v>27</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -7735,6 +8226,9 @@
           <t>b</t>
         </is>
       </c>
+      <c r="J164">
+        <v>27</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -7780,6 +8274,9 @@
           <t>b</t>
         </is>
       </c>
+      <c r="J165">
+        <v>27</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -7825,6 +8322,9 @@
           <t>b</t>
         </is>
       </c>
+      <c r="J166">
+        <v>27</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -7870,6 +8370,9 @@
           <t>b</t>
         </is>
       </c>
+      <c r="J167">
+        <v>27</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -7915,6 +8418,9 @@
           <t>b</t>
         </is>
       </c>
+      <c r="J168">
+        <v>27</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -7960,6 +8466,9 @@
           <t>b</t>
         </is>
       </c>
+      <c r="J169">
+        <v>27</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -8005,6 +8514,9 @@
           <t>b</t>
         </is>
       </c>
+      <c r="J170">
+        <v>27</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -8050,6 +8562,9 @@
           <t>b</t>
         </is>
       </c>
+      <c r="J171">
+        <v>27</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -8095,6 +8610,9 @@
           <t>u</t>
         </is>
       </c>
+      <c r="J172">
+        <v>27</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -8140,6 +8658,9 @@
           <t>u</t>
         </is>
       </c>
+      <c r="J173">
+        <v>27</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -8185,6 +8706,9 @@
           <t>u</t>
         </is>
       </c>
+      <c r="J174">
+        <v>27</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -8230,6 +8754,9 @@
           <t>u</t>
         </is>
       </c>
+      <c r="J175">
+        <v>27</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -8275,6 +8802,9 @@
           <t>u</t>
         </is>
       </c>
+      <c r="J176">
+        <v>27</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -8320,6 +8850,9 @@
           <t>u</t>
         </is>
       </c>
+      <c r="J177">
+        <v>27</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -8365,6 +8898,9 @@
           <t>u</t>
         </is>
       </c>
+      <c r="J178">
+        <v>27</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -8410,6 +8946,9 @@
           <t>u</t>
         </is>
       </c>
+      <c r="J179">
+        <v>27</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -8455,6 +8994,9 @@
           <t>u</t>
         </is>
       </c>
+      <c r="J180">
+        <v>27</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -8500,6 +9042,9 @@
           <t>u</t>
         </is>
       </c>
+      <c r="J181">
+        <v>27</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -8545,6 +9090,9 @@
           <t>b</t>
         </is>
       </c>
+      <c r="J182">
+        <v>55</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -8590,6 +9138,9 @@
           <t>b</t>
         </is>
       </c>
+      <c r="J183">
+        <v>55</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -8635,6 +9186,9 @@
           <t>b</t>
         </is>
       </c>
+      <c r="J184">
+        <v>55</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -8680,6 +9234,9 @@
           <t>b</t>
         </is>
       </c>
+      <c r="J185">
+        <v>55</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -8725,6 +9282,9 @@
           <t>b</t>
         </is>
       </c>
+      <c r="J186">
+        <v>55</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -8770,6 +9330,9 @@
           <t>b</t>
         </is>
       </c>
+      <c r="J187">
+        <v>55</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -8815,6 +9378,9 @@
           <t>b</t>
         </is>
       </c>
+      <c r="J188">
+        <v>55</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -8860,6 +9426,9 @@
           <t>b</t>
         </is>
       </c>
+      <c r="J189">
+        <v>55</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -8905,6 +9474,9 @@
           <t>b</t>
         </is>
       </c>
+      <c r="J190">
+        <v>55</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -8949,6 +9521,9 @@
         <is>
           <t>b</t>
         </is>
+      </c>
+      <c r="J191">
+        <v>55</v>
       </c>
     </row>
     <row r="192">
